--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2024_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2024_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 20:36</t>
+    <t xml:space="preserve">2026-08-02 20:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2024_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2024_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 20:08</t>
+    <t xml:space="preserve">2026-08-05 11:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2024_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2024_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 11:05</t>
+    <t xml:space="preserve">2026-08-16 10:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2024_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2024_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 10:12</t>
+    <t xml:space="preserve">2026-08-19 14:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2024_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2024_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 14:38</t>
+    <t xml:space="preserve">2026-08-28 12:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2024_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2024_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 12:36</t>
+    <t xml:space="preserve">2026-09-06 17:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
